--- a/data/trans_orig/IP07_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP07_R-Edad-trans_orig.xlsx
@@ -538,13 +538,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores cuya salud general, percibida por el adulto, es muy buena o excelente en 2007 (tasa de respuesta: 99,81%)</t>
+          <t>Menores cuya salud general, percibida por el/la adulto/a, es muy buena o excelente en 2007 (tasa de respuesta: 99,81%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -723,72 +723,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>142</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>94428</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>85958</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>101330</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>77,8%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>70,82%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>83,48%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>137</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>89487</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>82819</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>94880</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>83018</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>94931</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>84,29%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>78,01%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>89,37%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>142</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>94428</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>87034</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>101546</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>77,8%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>71,7%</t>
+          <t>78,19%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>83,66%</t>
+          <t>89,41%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>174194</t>
+          <t>173684</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>193787</t>
+          <t>192914</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>76,55%</t>
+          <t>76,33%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>85,16%</t>
+          <t>84,78%</t>
         </is>
       </c>
     </row>
@@ -836,72 +836,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>26952</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>20050</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>35422</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>22,2%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>16,52%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>29,18%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>16684</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>11291</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>23352</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>11240</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>23153</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>15,71%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>10,63%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>21,99%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>26952</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>19834</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>34346</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>22,2%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>28,3%</t>
+          <t>21,81%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>33764</t>
+          <t>34637</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>53357</t>
+          <t>53867</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>15,22%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>23,45%</t>
+          <t>23,67%</t>
         </is>
       </c>
     </row>
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>182</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>121380</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>121380</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>121380</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>162</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>106171</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>106171</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>106171</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>182</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>121380</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>121380</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>121380</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1066,72 +1066,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>291</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>193010</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>181533</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>203399</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>76,51%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>71,96%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>80,63%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>289</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>193785</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>181983</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>204718</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>182202</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>203740</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>76,53%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>71,87%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>80,85%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>291</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>193010</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>181455</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>203363</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>76,51%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>71,93%</t>
+          <t>71,96%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>80,62%</t>
+          <t>80,46%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>371856</t>
+          <t>371326</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>403880</t>
+          <t>402177</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>73,57%</t>
+          <t>73,46%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>79,9%</t>
+          <t>79,57%</t>
         </is>
       </c>
     </row>
@@ -1179,72 +1179,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>59247</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>48858</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>70724</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>23,49%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>19,37%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>28,04%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>90</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>59420</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>48487</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>71222</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>49465</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>71003</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>23,47%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>19,15%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>28,13%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>59247</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>48894</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>70802</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>23,49%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>19,38%</t>
+          <t>19,54%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>28,07%</t>
+          <t>28,04%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>101582</t>
+          <t>103285</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>133606</t>
+          <t>134136</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>20,1%</t>
+          <t>20,43%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>26,43%</t>
+          <t>26,54%</t>
         </is>
       </c>
     </row>
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>380</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>252257</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>252257</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>252257</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>379</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>253205</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>253205</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>253205</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>380</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>252257</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>252257</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>252257</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1409,72 +1409,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>156</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>104513</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>95662</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>112850</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>73,85%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>67,6%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>79,74%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>145</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>97448</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>88755</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>104425</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>88923</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>104100</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>76,4%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>69,59%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>81,87%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>156</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>104513</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>95461</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>112376</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>73,85%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>67,46%</t>
+          <t>69,72%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>79,41%</t>
+          <t>81,62%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>191040</t>
+          <t>190771</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>212919</t>
+          <t>212204</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>71,0%</t>
+          <t>70,9%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>79,13%</t>
+          <t>78,87%</t>
         </is>
       </c>
     </row>
@@ -1522,72 +1522,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>37002</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>28665</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>45853</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>26,15%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>20,26%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>32,4%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>46</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>30100</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>23123</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>38793</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>23448</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>38625</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>23,6%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>18,13%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>30,41%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>37002</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>29139</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>46054</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>26,15%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>20,59%</t>
+          <t>18,38%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>32,54%</t>
+          <t>30,28%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>56144</t>
+          <t>56859</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>78023</t>
+          <t>78292</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>20,87%</t>
+          <t>21,13%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>29,0%</t>
+          <t>29,1%</t>
         </is>
       </c>
     </row>
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>141515</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>141515</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>141515</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>191</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>127548</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>127548</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>127548</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>212</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>141515</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>141515</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>141515</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1752,72 +1752,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>241</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>160073</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>149480</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>168991</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>78,18%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>73,01%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>82,54%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>216</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>147750</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>137800</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>156427</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>137442</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>156831</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>76,12%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>71,0%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>80,59%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>241</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>160073</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>150314</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>168865</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>78,18%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>73,42%</t>
+          <t>70,81%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>82,48%</t>
+          <t>80,8%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>293964</t>
+          <t>293797</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>321173</t>
+          <t>320624</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>73,71%</t>
+          <t>73,66%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>80,53%</t>
+          <t>80,39%</t>
         </is>
       </c>
     </row>
@@ -1865,72 +1865,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>44665</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>35747</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>55258</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>21,82%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>17,46%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>26,99%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>70</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>46347</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>37670</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>56297</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>37266</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>56655</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>23,88%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>19,41%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>29,0%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>44665</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>35873</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>54424</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>21,82%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>17,52%</t>
+          <t>19,2%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>26,58%</t>
+          <t>29,19%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>77662</t>
+          <t>78211</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>104871</t>
+          <t>105038</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>19,47%</t>
+          <t>19,61%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>26,29%</t>
+          <t>26,34%</t>
         </is>
       </c>
     </row>
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>308</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>204738</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>204738</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>204738</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>286</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>194097</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>194097</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>194097</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>308</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>204738</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>204738</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>204738</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2095,72 +2095,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>830</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>552024</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>531032</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>569418</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>76,68%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>73,77%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>79,1%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>787</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>528471</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>510969</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>544993</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>509734</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>544114</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>77,6%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>75,03%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>80,03%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>830</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>552024</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>533092</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>570402</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>76,68%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>74,05%</t>
+          <t>74,85%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>79,23%</t>
+          <t>79,9%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1055193</t>
+          <t>1057138</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1105701</t>
+          <t>1107039</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>75,32%</t>
+          <t>75,46%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>78,93%</t>
+          <t>79,02%</t>
         </is>
       </c>
     </row>
@@ -2208,72 +2208,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>252</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>167866</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>150472</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>188858</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>23,32%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>20,9%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>26,23%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>231</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>152550</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>136028</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>170052</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>136907</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>171287</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>22,4%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>19,97%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>24,97%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>252</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>167866</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>149488</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>186798</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>23,32%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>20,77%</t>
+          <t>20,1%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>25,95%</t>
+          <t>25,15%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>295210</t>
+          <t>293872</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>345718</t>
+          <t>343773</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>20,98%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>24,68%</t>
+          <t>24,54%</t>
         </is>
       </c>
     </row>
@@ -2321,57 +2321,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1082</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>719890</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>719890</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>719890</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1018</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>681021</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1082</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>719890</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>719890</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>719890</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2485,13 +2485,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores cuya salud general, percibida por el adulto, es muy buena o excelente en 2012 (tasa de respuesta: 99,62%)</t>
+          <t>Menores cuya salud general, percibida por el/la adulto/a, es muy buena o excelente en 2012 (tasa de respuesta: 99,62%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2502,7 +2502,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2670,72 +2670,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>106179</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>97031</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>114672</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>73,09%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>66,79%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>78,93%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>167</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>112021</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>102775</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>120070</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>102684</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>119634</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>76,33%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>70,03%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>81,81%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>106179</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>96484</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>114662</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>73,09%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>66,41%</t>
+          <t>69,97%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>78,93%</t>
+          <t>81,52%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>205478</t>
+          <t>205450</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>229558</t>
+          <t>229921</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>70,36%</t>
+          <t>70,35%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>78,61%</t>
+          <t>78,73%</t>
         </is>
       </c>
     </row>
@@ -2783,72 +2783,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>39096</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>30603</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>48244</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>26,91%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>21,07%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>33,21%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>52</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>34740</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>26691</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>43986</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>27127</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>44077</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>23,67%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>18,19%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>29,97%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>39096</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>30613</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>48791</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>26,91%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>18,48%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>33,59%</t>
+          <t>30,03%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>62477</t>
+          <t>62114</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>86557</t>
+          <t>86585</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>21,39%</t>
+          <t>21,27%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>29,64%</t>
+          <t>29,65%</t>
         </is>
       </c>
     </row>
@@ -2896,57 +2896,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>206</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>145275</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>145275</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>145275</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>219</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>146761</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>146761</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>146761</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>206</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>145275</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>145275</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>145275</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3013,72 +3013,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>284</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>202707</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>190430</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>214145</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>76,19%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>71,58%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>80,49%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>265</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>184106</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>173860</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>194033</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>173960</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>194603</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>78,42%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>74,06%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>82,65%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>284</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>202707</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>191163</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>214212</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>76,19%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>71,85%</t>
+          <t>74,1%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>80,52%</t>
+          <t>82,89%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>370310</t>
+          <t>371474</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>402069</t>
+          <t>401640</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>73,94%</t>
+          <t>74,17%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>80,28%</t>
+          <t>80,2%</t>
         </is>
       </c>
     </row>
@@ -3126,72 +3126,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>63338</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>51900</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>75615</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>23,81%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>19,51%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>28,42%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>73</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>50659</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>40732</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>60905</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>40162</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>60805</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>21,58%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>17,35%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>25,94%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>63338</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>51833</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>74882</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>23,81%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>19,48%</t>
+          <t>17,11%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>28,15%</t>
+          <t>25,9%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>98741</t>
+          <t>99170</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>130500</t>
+          <t>129336</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>19,72%</t>
+          <t>19,8%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>26,06%</t>
+          <t>25,83%</t>
         </is>
       </c>
     </row>
@@ -3239,57 +3239,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>370</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>266045</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>266045</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>266045</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>338</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>234765</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>234765</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>234765</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>370</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>266045</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>266045</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>266045</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3356,72 +3356,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>169</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>117137</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>108415</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>126543</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>73,87%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>68,37%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>79,8%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>161</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>112621</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>102661</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>121998</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>103069</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>121438</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>71,71%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>65,37%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>77,68%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>169</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>117137</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>108142</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>126252</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>73,87%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>68,2%</t>
+          <t>65,63%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>79,62%</t>
+          <t>77,33%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>216314</t>
+          <t>216090</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>242719</t>
+          <t>242280</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>68,54%</t>
+          <t>68,47%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>76,9%</t>
+          <t>76,76%</t>
         </is>
       </c>
     </row>
@@ -3469,72 +3469,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>41434</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>32028</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>50156</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>26,13%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>20,2%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>31,63%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>62</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>44422</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>35045</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>54382</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>35605</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>53974</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>28,29%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>22,32%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>34,63%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>41434</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>32319</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>50429</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>26,13%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>20,38%</t>
+          <t>22,67%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>31,8%</t>
+          <t>34,37%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>72895</t>
+          <t>73334</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>99300</t>
+          <t>99524</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>23,1%</t>
+          <t>23,24%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>31,46%</t>
+          <t>31,53%</t>
         </is>
       </c>
     </row>
@@ -3582,57 +3582,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>228</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>158571</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>158571</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>158571</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>223</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>157043</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>157043</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>157043</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>228</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>158571</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>158571</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>158571</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3699,72 +3699,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>198</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>134292</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>124347</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>143351</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>74,63%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>69,1%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>79,66%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>177</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>124890</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>113385</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>133596</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>115253</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>134635</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>73,21%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>66,46%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>78,31%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>198</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>134292</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>124650</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>143034</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>74,63%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>69,27%</t>
+          <t>67,56%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>79,48%</t>
+          <t>78,92%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>246442</t>
+          <t>245116</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>272676</t>
+          <t>271752</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>70,3%</t>
+          <t>69,92%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>77,78%</t>
+          <t>77,52%</t>
         </is>
       </c>
     </row>
@@ -3812,72 +3812,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>45663</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>36604</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>55608</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>25,37%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>20,34%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>30,9%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>65</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>45711</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>37005</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>57216</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>35966</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>55348</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>26,79%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>21,69%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>33,54%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>45663</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>36921</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>55305</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>25,37%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>20,52%</t>
+          <t>21,08%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>30,73%</t>
+          <t>32,44%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>77880</t>
+          <t>78804</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>104114</t>
+          <t>105440</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>22,22%</t>
+          <t>22,48%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>29,7%</t>
+          <t>30,08%</t>
         </is>
       </c>
     </row>
@@ -3925,57 +3925,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>265</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>179955</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>179955</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>179955</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>242</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>170601</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>170601</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>170601</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>265</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>179955</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>179955</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>179955</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4042,72 +4042,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>801</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>560316</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>539212</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>577892</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>74,72%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>71,91%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>77,07%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>770</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>533639</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>514352</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>551741</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>513145</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>553843</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>75,25%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>72,53%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>77,8%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>801</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>560316</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>538961</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>579701</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>74,72%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>71,88%</t>
+          <t>72,36%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>77,31%</t>
+          <t>78,1%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1065909</t>
+          <t>1066253</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1119379</t>
+          <t>1120739</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>73,06%</t>
+          <t>73,08%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>76,72%</t>
+          <t>76,81%</t>
         </is>
       </c>
     </row>
@@ -4155,72 +4155,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>268</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>189530</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>171954</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>210634</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>25,28%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>22,93%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>28,09%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>252</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>175531</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>157429</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>194818</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>155327</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>196025</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>24,75%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>22,2%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>27,47%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>268</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>189530</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>170145</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>210885</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>25,28%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>22,69%</t>
+          <t>21,9%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>28,12%</t>
+          <t>27,64%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>339637</t>
+          <t>338277</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>393107</t>
+          <t>392763</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>23,28%</t>
+          <t>23,19%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>26,94%</t>
+          <t>26,92%</t>
         </is>
       </c>
     </row>
@@ -4268,57 +4268,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1069</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>749846</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>749846</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>749846</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1022</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>709170</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>709170</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>709170</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1069</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>749846</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>749846</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>749846</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4432,13 +4432,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores cuya salud general, percibida por el adulto, es muy buena o excelente en 2016 (tasa de respuesta: 99,48%)</t>
+          <t>Menores cuya salud general, percibida por el/la adulto/a, es muy buena o excelente en 2016 (tasa de respuesta: 99,48%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4449,7 +4449,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4617,72 +4617,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>108373</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>100989</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>113435</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>87,83%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>81,84%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>91,93%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>184</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>115180</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>108883</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>120068</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>107588</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>119941</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>87,97%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>83,16%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>91,7%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>165</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>108373</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>100601</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>113777</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>87,83%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>81,53%</t>
+          <t>82,17%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>92,21%</t>
+          <t>91,61%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>213633</t>
+          <t>214812</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>231068</t>
+          <t>231229</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>84,0%</t>
+          <t>84,46%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>90,86%</t>
+          <t>90,92%</t>
         </is>
       </c>
     </row>
@@ -4730,72 +4730,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>15023</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>9961</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>22407</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>12,17%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>8,07%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>18,16%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>15749</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>10861</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>22046</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>10988</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>23341</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>12,03%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>8,3%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>16,84%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>15023</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>9619</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>22795</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>12,17%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>18,47%</t>
+          <t>17,83%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>23257</t>
+          <t>23096</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>40692</t>
+          <t>39513</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>15,54%</t>
         </is>
       </c>
     </row>
@@ -4843,57 +4843,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>186</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>123396</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>123396</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>123396</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>210</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>130929</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>130929</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>130929</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>186</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>123396</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>123396</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>123396</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4960,72 +4960,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>332</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>225359</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>215981</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>233586</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>87,55%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>83,9%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>90,74%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>286</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>181493</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>173022</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>188242</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>171077</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>187580</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>87,22%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>83,15%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>90,46%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>332</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>225359</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>216182</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>233880</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>87,55%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>83,98%</t>
+          <t>82,22%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>90,86%</t>
+          <t>90,15%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>394296</t>
+          <t>394056</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>417476</t>
+          <t>417189</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>84,7%</t>
+          <t>84,65%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>89,68%</t>
+          <t>89,62%</t>
         </is>
       </c>
     </row>
@@ -5073,72 +5073,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>32056</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>23829</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>41434</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>12,45%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>9,26%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>16,1%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>42</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>26591</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>19842</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>35062</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>20504</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>37007</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>12,78%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>9,54%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>16,85%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>32056</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>23535</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>41233</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>12,45%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>17,78%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>48023</t>
+          <t>48310</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>71203</t>
+          <t>71443</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>15,35%</t>
         </is>
       </c>
     </row>
@@ -5186,57 +5186,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>379</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>257415</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>257415</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>257415</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>328</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>208084</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>208084</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>208084</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>379</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>257415</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>257415</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>257415</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5303,72 +5303,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>216</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>154649</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>144799</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>163046</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>82,01%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>76,79%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>86,46%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>240</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>167440</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>159132</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>173480</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>159097</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>173413</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>88,96%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>84,54%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>92,17%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>216</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>154649</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>144025</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>162078</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>82,01%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>76,38%</t>
+          <t>84,53%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>85,95%</t>
+          <t>92,13%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>309466</t>
+          <t>310457</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>332612</t>
+          <t>332633</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>82,13%</t>
+          <t>82,39%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>88,27%</t>
+          <t>88,28%</t>
         </is>
       </c>
     </row>
@@ -5416,72 +5416,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>33923</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>25526</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>43773</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>17,99%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>13,54%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>23,21%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>31</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>20784</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>14744</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>29092</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>14811</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>29127</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>11,04%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>7,83%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>15,46%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>33923</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>26494</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>44547</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>17,99%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>14,05%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>23,62%</t>
+          <t>15,47%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>44185</t>
+          <t>44164</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>67331</t>
+          <t>66340</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>17,87%</t>
+          <t>17,61%</t>
         </is>
       </c>
     </row>
@@ -5529,57 +5529,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>263</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>188572</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>188572</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>188572</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>271</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>188224</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>188224</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>188224</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>263</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>188572</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>188572</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>188572</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5646,72 +5646,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>201</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>149055</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>139968</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>155761</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>86,34%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>81,07%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>90,22%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>208</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>146014</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>137303</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>153015</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>137941</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>153286</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>84,63%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>79,58%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>88,69%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>201</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>149055</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>140989</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>155765</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>86,34%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>81,67%</t>
+          <t>79,95%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>90,22%</t>
+          <t>88,84%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>282668</t>
+          <t>283740</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>305636</t>
+          <t>306183</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>81,89%</t>
+          <t>82,2%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>88,54%</t>
+          <t>88,7%</t>
         </is>
       </c>
     </row>
@@ -5759,72 +5759,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>23586</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>16880</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>32673</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>13,66%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>9,78%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>18,93%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>26521</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>19520</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>35232</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>19249</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>34594</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>15,37%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>11,31%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>20,42%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>23586</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>16876</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>31652</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>13,66%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>18,33%</t>
+          <t>20,05%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>39541</t>
+          <t>38994</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>62509</t>
+          <t>61437</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>18,11%</t>
+          <t>17,8%</t>
         </is>
       </c>
     </row>
@@ -5872,57 +5872,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>233</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>172641</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>172641</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>172641</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>245</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>172535</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>172535</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>172535</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>233</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>172641</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>172641</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>172641</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5989,72 +5989,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>914</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>637436</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>621765</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>653037</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>85,91%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>83,79%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>88,01%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>918</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>610128</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>592800</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>623724</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>595178</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>622956</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>87,19%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>84,71%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>89,13%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>914</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>637436</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>620838</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>653042</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>85,91%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>83,67%</t>
+          <t>85,05%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>88,01%</t>
+          <t>89,02%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1226851</t>
+          <t>1226504</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1267830</t>
+          <t>1268462</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>85,09%</t>
+          <t>85,07%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>87,93%</t>
+          <t>87,98%</t>
         </is>
       </c>
     </row>
@@ -6102,72 +6102,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>147</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>104588</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>88987</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>120259</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>14,09%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>11,99%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>16,21%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>136</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>89645</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>76049</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>106973</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>76817</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>104595</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>12,81%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>10,87%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>15,29%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>147</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>104588</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>88982</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>121186</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>14,09%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>14,95%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>173967</t>
+          <t>173335</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>214946</t>
+          <t>215293</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>14,93%</t>
         </is>
       </c>
     </row>
@@ -6215,57 +6215,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1061</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>742024</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>742024</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>742024</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1054</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>699773</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>699773</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>699773</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1061</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>742024</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>742024</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>742024</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6379,13 +6379,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores cuya salud general, percibida por el adulto, es muy buena o excelente en 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Menores cuya salud general, percibida por el/la adulto/a, es muy buena o excelente en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -6396,7 +6396,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -6564,72 +6564,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>41300</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>37026</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>44854</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>81,72%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>73,27%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>88,75%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>89</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>46939</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>42314</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>50949</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>81,62%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>73,58%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>88,59%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>50795</t>
+          <t>42157</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>45752</t>
+          <t>36928</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>55422</t>
+          <t>45596</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>82,67%</t>
+          <t>80,93%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>74,46%</t>
+          <t>70,89%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>90,2%</t>
+          <t>87,53%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>97735</t>
+          <t>83457</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>90646</t>
+          <t>77436</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>103459</t>
+          <t>88461</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>82,16%</t>
+          <t>81,32%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>76,2%</t>
+          <t>75,45%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>86,97%</t>
+          <t>86,2%</t>
         </is>
       </c>
     </row>
@@ -6677,72 +6677,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>9237</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>5683</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>13511</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>18,28%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>11,25%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>26,73%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>10572</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>6562</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>15197</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>18,38%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>11,41%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>26,42%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>10649</t>
+          <t>9933</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6022</t>
+          <t>6494</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>15692</t>
+          <t>15162</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>19,07%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>25,54%</t>
+          <t>29,11%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>21220</t>
+          <t>19170</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>15496</t>
+          <t>14166</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>28309</t>
+          <t>25191</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>18,68%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>13,03%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>23,8%</t>
+          <t>24,55%</t>
         </is>
       </c>
     </row>
@@ -6790,57 +6790,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>50537</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>50537</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>50537</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>109</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>57511</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>57511</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>57511</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>61444</t>
+          <t>52090</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>61444</t>
+          <t>52090</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>61444</t>
+          <t>52090</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>118955</t>
+          <t>102627</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>118955</t>
+          <t>102627</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>118955</t>
+          <t>102627</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6907,72 +6907,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>122311</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>113667</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>130504</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>77,65%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>72,16%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>82,85%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>193</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>123028</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>114167</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>130745</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>77,23%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>71,67%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>82,08%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>212</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>141586</t>
+          <t>110606</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>131300</t>
+          <t>102224</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>150788</t>
+          <t>118076</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>77,56%</t>
+          <t>76,01%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>71,92%</t>
+          <t>70,25%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>82,6%</t>
+          <t>81,14%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>264614</t>
+          <t>232916</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>250172</t>
+          <t>221051</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>276889</t>
+          <t>245067</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>77,41%</t>
+          <t>76,86%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>73,18%</t>
+          <t>72,94%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>81,0%</t>
+          <t>80,87%</t>
         </is>
       </c>
     </row>
@@ -7020,72 +7020,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>35211</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>27018</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>43855</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>22,35%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>17,15%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>27,84%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>65</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>36271</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>28554</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>45132</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>22,77%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>17,92%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>28,33%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>40968</t>
+          <t>34912</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>31766</t>
+          <t>27442</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>51254</t>
+          <t>43294</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>22,44%</t>
+          <t>23,99%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>18,86%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>28,08%</t>
+          <t>29,75%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>77239</t>
+          <t>70123</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>64964</t>
+          <t>57972</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>91681</t>
+          <t>81988</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>23,14%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>19,0%</t>
+          <t>19,13%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>26,82%</t>
+          <t>27,06%</t>
         </is>
       </c>
     </row>
@@ -7133,57 +7133,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>276</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>157522</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>157522</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>157522</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>258</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>276</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>182554</t>
+          <t>145518</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>182554</t>
+          <t>145518</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>182554</t>
+          <t>145518</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>341853</t>
+          <t>303039</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>341853</t>
+          <t>303039</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>341853</t>
+          <t>303039</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7250,72 +7250,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>179</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>148622</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>137720</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>160110</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>74,26%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>68,82%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>80,0%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>169</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>128644</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>117774</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>138101</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>73,98%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>67,73%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>79,42%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>179</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>157611</t>
+          <t>128951</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>143023</t>
+          <t>119086</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>169433</t>
+          <t>139139</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>74,17%</t>
+          <t>73,47%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>67,31%</t>
+          <t>67,85%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>79,74%</t>
+          <t>79,27%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>286255</t>
+          <t>277573</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>269220</t>
+          <t>262006</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>301231</t>
+          <t>292457</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>74,09%</t>
+          <t>73,89%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>69,68%</t>
+          <t>69,75%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>77,96%</t>
+          <t>77,85%</t>
         </is>
       </c>
     </row>
@@ -7363,72 +7363,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>51504</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>40016</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>62406</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>25,74%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>20,0%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>31,18%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>65</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>45244</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>35787</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>56114</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>26,02%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>20,58%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>32,27%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>54879</t>
+          <t>46567</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>43057</t>
+          <t>36379</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>69467</t>
+          <t>56432</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>25,83%</t>
+          <t>26,53%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>20,26%</t>
+          <t>20,73%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>32,69%</t>
+          <t>32,15%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>100123</t>
+          <t>98071</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>85147</t>
+          <t>83187</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>117158</t>
+          <t>113638</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>25,91%</t>
+          <t>26,11%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>22,04%</t>
+          <t>22,15%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>30,32%</t>
+          <t>30,25%</t>
         </is>
       </c>
     </row>
@@ -7476,57 +7476,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>243</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>234</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>173888</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>173888</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>173888</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>243</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>175518</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>175518</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>175518</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>386378</t>
+          <t>375644</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>386378</t>
+          <t>375644</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>386378</t>
+          <t>375644</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7593,72 +7593,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>259</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>218488</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>194838</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>233085</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>74,66%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>66,58%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>79,65%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>261</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>216235</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>198406</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>231527</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>78,5%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>72,03%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>84,05%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>259</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>229686</t>
+          <t>199531</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>201272</t>
+          <t>186523</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>245058</t>
+          <t>209741</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>75,19%</t>
+          <t>77,77%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>65,89%</t>
+          <t>72,7%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>80,22%</t>
+          <t>81,75%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>445920</t>
+          <t>418019</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>417639</t>
+          <t>390961</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>470324</t>
+          <t>436842</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>76,76%</t>
+          <t>76,11%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>71,89%</t>
+          <t>71,19%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>80,96%</t>
+          <t>79,54%</t>
         </is>
       </c>
     </row>
@@ -7706,72 +7706,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>74157</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>59560</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>97807</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>25,34%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>20,35%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>33,42%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>81</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>59223</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>43931</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>77052</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>21,5%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>15,95%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>27,97%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>75797</t>
+          <t>57022</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>60425</t>
+          <t>46812</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>104211</t>
+          <t>70030</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>24,81%</t>
+          <t>22,23%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19,78%</t>
+          <t>18,25%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>34,11%</t>
+          <t>27,3%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>135020</t>
+          <t>131179</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>110616</t>
+          <t>112356</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>163301</t>
+          <t>158237</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>23,24%</t>
+          <t>23,89%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>19,04%</t>
+          <t>20,46%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>28,11%</t>
+          <t>28,81%</t>
         </is>
       </c>
     </row>
@@ -7824,17 +7824,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>275458</t>
+          <t>292645</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>275458</t>
+          <t>292645</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>275458</t>
+          <t>292645</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7859,17 +7859,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>305483</t>
+          <t>256553</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>305483</t>
+          <t>256553</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>305483</t>
+          <t>256553</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>580940</t>
+          <t>549198</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>580940</t>
+          <t>549198</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>580940</t>
+          <t>549198</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7936,72 +7936,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>749</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>530720</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>503826</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>550622</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>75,73%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>71,89%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>78,57%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>712</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>514845</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>493501</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>538549</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>77,29%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>74,08%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>80,84%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>749</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>579679</t>
+          <t>481245</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>546755</t>
+          <t>462596</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>600807</t>
+          <t>497545</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>76,08%</t>
+          <t>76,43%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>71,76%</t>
+          <t>73,47%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>78,85%</t>
+          <t>79,02%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1094524</t>
+          <t>1011965</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1056234</t>
+          <t>977554</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1124260</t>
+          <t>1039155</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>76,64%</t>
+          <t>76,06%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>73,96%</t>
+          <t>73,47%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>78,72%</t>
+          <t>78,1%</t>
         </is>
       </c>
     </row>
@@ -8049,72 +8049,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>228</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>170109</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>150207</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>197003</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>24,27%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>21,43%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>28,11%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>231</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>151310</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>127606</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>172654</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>22,71%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>19,16%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>25,92%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>228</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>182293</t>
+          <t>148433</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>161165</t>
+          <t>132133</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>215217</t>
+          <t>167082</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>23,92%</t>
+          <t>23,57%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>21,15%</t>
+          <t>20,98%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>28,24%</t>
+          <t>26,53%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>333603</t>
+          <t>318543</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>303867</t>
+          <t>291353</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>371893</t>
+          <t>352954</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>23,36%</t>
+          <t>23,94%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>21,28%</t>
+          <t>21,9%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>26,04%</t>
+          <t>26,53%</t>
         </is>
       </c>
     </row>
@@ -8162,57 +8162,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>977</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>700829</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>700829</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>700829</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>943</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>666155</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>666155</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>666155</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>977</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>761972</t>
+          <t>629678</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>761972</t>
+          <t>629678</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>761972</t>
+          <t>629678</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1428127</t>
+          <t>1330508</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1428127</t>
+          <t>1330508</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1428127</t>
+          <t>1330508</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
